--- a/artfynd/A 43967-2024 artfynd.xlsx
+++ b/artfynd/A 43967-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89564654</v>
+        <v>89564612</v>
       </c>
       <c r="B2" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>399105.8448705007</v>
+        <v>399430</v>
       </c>
       <c r="R2" t="n">
-        <v>7082327.078438163</v>
+        <v>7082877</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,34 +743,20 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Granbas</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89564685</v>
+        <v>89564654</v>
       </c>
       <c r="B3" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399111.9112694118</v>
+        <v>399106</v>
       </c>
       <c r="R3" t="n">
-        <v>7082227.127983216</v>
+        <v>7082327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,21 +845,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Granbas</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,37 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89564641</v>
+        <v>89564696</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>399383.7802895622</v>
+        <v>399124</v>
       </c>
       <c r="R4" t="n">
-        <v>7082586.943220415</v>
+        <v>7082197</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,21 +951,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,6 +964,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Gran, gammalt savflöde</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1028,37 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89564608</v>
+        <v>89564618</v>
       </c>
       <c r="B5" t="n">
-        <v>95187</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2389</v>
+        <v>1841</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>399022.8481382519</v>
+        <v>399259</v>
       </c>
       <c r="R5" t="n">
-        <v>7082535.871162427</v>
+        <v>7082455</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,19 +1057,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,53 +1090,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89564667</v>
+        <v>89564673</v>
       </c>
       <c r="B6" t="n">
-        <v>77698</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230552</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjaajatjaeltjie, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>399186.0501808651</v>
+        <v>399098</v>
       </c>
       <c r="R6" t="n">
-        <v>7082099.825029819</v>
+        <v>7082409</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,35 +1158,19 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1269,37 +1191,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89564612</v>
+        <v>89564680</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>2387</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>399430.2100588455</v>
+        <v>399440</v>
       </c>
       <c r="R7" t="n">
-        <v>7082877.172041403</v>
+        <v>7082916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,28 +1259,17 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1386,15 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89564675</v>
+        <v>89564608</v>
       </c>
       <c r="B8" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>2389</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>399117.9063470789</v>
+        <v>399023</v>
       </c>
       <c r="R8" t="n">
-        <v>7082234.880388231</v>
+        <v>7082536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,19 +1360,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1502,15 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89564680</v>
+        <v>89564649</v>
       </c>
       <c r="B9" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2387</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1542,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>399439.8554988671</v>
+        <v>399021</v>
       </c>
       <c r="R9" t="n">
-        <v>7082916.138872279</v>
+        <v>7082549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,19 +1461,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,37 +1494,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89564696</v>
+        <v>89564685</v>
       </c>
       <c r="B10" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1658,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>399124.2068323343</v>
+        <v>399112</v>
       </c>
       <c r="R10" t="n">
-        <v>7082197.158443677</v>
+        <v>7082227</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,21 +1562,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1714,11 +1575,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Gran, gammalt savflöde</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1739,15 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89564673</v>
+        <v>89564675</v>
       </c>
       <c r="B11" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,21 +1606,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2387</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1779,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>399097.8729137954</v>
+        <v>399118</v>
       </c>
       <c r="R11" t="n">
-        <v>7082408.990668342</v>
+        <v>7082235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,19 +1663,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,16 +1699,11 @@
         <v>89564663</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1895,10 +1731,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>399126.0883100738</v>
+        <v>399126</v>
       </c>
       <c r="R12" t="n">
-        <v>7082186.945575028</v>
+        <v>7082187</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,19 +1764,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,15 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89564618</v>
+        <v>89564670</v>
       </c>
       <c r="B13" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1841</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2011,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>399258.8964772308</v>
+        <v>399333</v>
       </c>
       <c r="R13" t="n">
-        <v>7082455.013642439</v>
+        <v>7082514</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,19 +1865,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,15 +1898,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89564670</v>
+        <v>89564655</v>
       </c>
       <c r="B14" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,21 +1909,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2127,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>399332.8266712868</v>
+        <v>399274</v>
       </c>
       <c r="R14" t="n">
-        <v>7082513.989434103</v>
+        <v>7082842</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,19 +1966,9 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-08-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2203,15 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89564649</v>
+        <v>89564705</v>
       </c>
       <c r="B15" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,21 +2010,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2243,10 +2034,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>399021.0666203001</v>
+        <v>399103</v>
       </c>
       <c r="R15" t="n">
-        <v>7082549.169291001</v>
+        <v>7082622</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,21 +2067,11 @@
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-08-02</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2299,6 +2080,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Grankvist</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2312,6 +2098,318 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>89564641</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjaajatjaeltjie, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>399384</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7082587</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-08-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>89564713</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tjaajatjaeltjie, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>399275</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7082844</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-08-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>89564667</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjaajatjaeltjie, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>399186</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7082100</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-07-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-08-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 43967-2024 artfynd.xlsx
+++ b/artfynd/A 43967-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564612</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564654</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564696</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564618</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564673</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564680</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564608</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564649</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564685</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564675</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564663</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564670</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564655</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564705</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564641</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2302,6 +2382,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564713</t>
         </is>
       </c>
     </row>
@@ -2414,8 +2499,32 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564667</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>